--- a/data/trans_orig/P79_n_R3-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R3-Clase-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>16071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>21391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26936</t>
+          <t>32159</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17954</t>
+          <t>21159</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39521</t>
+          <t>47108</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30432</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>48955</t>
+          <t>58065</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37631</t>
+          <t>44576</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64569</t>
+          <t>74919</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>471356</t>
+          <t>509611</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>457882</t>
+          <t>494238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>480935</t>
+          <t>521284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>420422</t>
+          <t>456155</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>411352</t>
+          <t>444629</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>428277</t>
+          <t>465032</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>891778</t>
+          <t>965766</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>874616</t>
+          <t>946739</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>904195</t>
+          <t>980578</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>889</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>896</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>12840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>21364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33377</t>
+          <t>36413</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>25599</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45841</t>
+          <t>51130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39461</t>
+          <t>44515</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29736</t>
+          <t>34395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>57502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>72838</t>
+          <t>80928</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>65898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87902</t>
+          <t>97797</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>410070</t>
+          <t>437378</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>395132</t>
+          <t>422345</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>420164</t>
+          <t>449243</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>336665</t>
+          <t>371585</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>324643</t>
+          <t>357578</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347285</t>
+          <t>382532</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>746736</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>729289</t>
+          <t>790841</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>761667</t>
+          <t>825721</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23274</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42264</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>30069</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>39791</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>37228</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75230</t>
+          <t>63199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>24993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>67966</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>53829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85986</t>
+          <t>84511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>599469</t>
+          <t>391794</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>550416</t>
+          <t>374498</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>643958</t>
+          <t>406361</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>148683</t>
+          <t>165550</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140982</t>
+          <t>157664</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154148</t>
+          <t>172565</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>748152</t>
+          <t>557344</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706163</t>
+          <t>537847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>793942</t>
+          <t>575265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19978</t>
+          <t>19074</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>808</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21541</t>
+          <t>21760</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>38091</t>
+          <t>45069</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55363</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>12207</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26650</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>54544</t>
+          <t>63751</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36672</t>
+          <t>48081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73015</t>
+          <t>81429</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>113104</t>
+          <t>129626</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91311</t>
+          <t>106553</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>134784</t>
+          <t>156012</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57518</t>
+          <t>70101</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28235</t>
+          <t>57029</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78129</t>
+          <t>84930</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>170622</t>
+          <t>199726</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>120566</t>
+          <t>175291</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>207151</t>
+          <t>234866</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>875733</t>
+          <t>949189</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>849577</t>
+          <t>919669</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>901038</t>
+          <t>975262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>901172</t>
+          <t>769286</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>873638</t>
+          <t>752663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>937766</t>
+          <t>783479</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1776905</t>
+          <t>1718475</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1733310</t>
+          <t>1681744</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1847371</t>
+          <t>1749558</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>14699</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>23295</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23579</t>
+          <t>27054</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35030</t>
+          <t>39392</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>42674</t>
+          <t>53306</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29801</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57184</t>
+          <t>67659</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>66254</t>
+          <t>80360</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48607</t>
+          <t>64999</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84599</t>
+          <t>100201</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>55499</t>
+          <t>72170</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43466</t>
+          <t>56679</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72613</t>
+          <t>92800</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>87709</t>
+          <t>98777</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66287</t>
+          <t>83649</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107241</t>
+          <t>115486</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>143209</t>
+          <t>170947</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>117534</t>
+          <t>148626</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>167242</t>
+          <t>194760</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>390319</t>
+          <t>462713</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>371909</t>
+          <t>441075</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>404429</t>
+          <t>480164</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>703957</t>
+          <t>669898</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>679266</t>
+          <t>649328</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>737354</t>
+          <t>689516</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1094276</t>
+          <t>1132611</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1064934</t>
+          <t>1103708</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1137608</t>
+          <t>1160089</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28546</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>34635</t>
+          <t>39685</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24548</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44552</t>
+          <t>52772</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>47068</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53190</t>
+          <t>63661</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32501</t>
+          <t>30256</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>85931</t>
+          <t>101081</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>70356</t>
+          <t>83419</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>103251</t>
+          <t>119149</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>96785</t>
+          <t>113528</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>79404</t>
+          <t>92878</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>118147</t>
+          <t>135881</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>224672</t>
+          <t>217399</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>204599</t>
+          <t>199586</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>234587</t>
+          <t>227679</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>631532</t>
+          <t>696174</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>610636</t>
+          <t>672863</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>649956</t>
+          <t>715474</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>856203</t>
+          <t>913573</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>830184</t>
+          <t>886009</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>880034</t>
+          <t>937340</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,102 +4139,102 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>20981</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10620</t>
+          <t>12199</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>33641</t>
+          <t>33687</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>21386</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>13735</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>33773</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>42367</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>29835</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>58128</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>20614</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>12459</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>38521</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>40822</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>27728</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>61501</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>101238</t>
+          <t>120201</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>77697</t>
+          <t>99411</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>126193</t>
+          <t>145314</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>107316</t>
+          <t>127409</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>85794</t>
+          <t>106953</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>128831</t>
+          <t>150034</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>208555</t>
+          <t>247610</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>175090</t>
+          <t>217744</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>241140</t>
+          <t>278658</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>282995</t>
+          <t>333211</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>222973</t>
+          <t>295073</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>324780</t>
+          <t>372003</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>307395</t>
+          <t>357949</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>255511</t>
+          <t>327608</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>345697</t>
+          <t>391702</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>590390</t>
+          <t>691160</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>506773</t>
+          <t>637992</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>647706</t>
+          <t>740940</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2971618</t>
+          <t>2968082</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2919258</t>
+          <t>2922264</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3050934</t>
+          <t>3010494</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3142433</t>
+          <t>3128649</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3095395</t>
+          <t>3088226</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3219290</t>
+          <t>3167400</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>6114051</t>
+          <t>6096731</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6037360</t>
+          <t>6042440</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6223726</t>
+          <t>6162358</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>87,07%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
